--- a/ResourcesBD/OutletExcel.xlsx
+++ b/ResourcesBD/OutletExcel.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Excel Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentManualCount="8"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="143">
   <si>
     <t/>
   </si>
@@ -291,9 +291,6 @@
     <t>CA000</t>
   </si>
   <si>
-    <t>00002</t>
-  </si>
-  <si>
     <t>আলিফ প্লাজা সুপার মার্কেট চক বাজার কাঁচা বাজার</t>
   </si>
   <si>
@@ -445,6 +442,12 @@
   </si>
   <si>
     <t>Md.Sahabuddin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00001 </t>
+  </si>
+  <si>
+    <t>00001</t>
   </si>
 </sst>
 </file>
@@ -483,11 +486,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -782,7 +786,9 @@
     <col min="23" max="23" width="8" style="1"/>
     <col min="32" max="32" width="8" style="2"/>
     <col min="35" max="35" width="8" style="1"/>
-    <col min="39" max="46" width="8" style="1"/>
+    <col min="39" max="43" width="8" style="1"/>
+    <col min="44" max="44" width="12.08984375" style="1" customWidth="1"/>
+    <col min="45" max="46" width="8" style="1"/>
     <col min="48" max="69" width="8" style="1"/>
     <col min="70" max="71" width="8" style="2"/>
     <col min="74" max="75" width="8" style="1"/>
@@ -1017,16 +1023,16 @@
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
@@ -1035,13 +1041,13 @@
         <v>77</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" t="s">
         <v>103</v>
-      </c>
-      <c r="I2" t="s">
-        <v>104</v>
       </c>
       <c r="J2" t="s">
         <v>78</v>
@@ -1074,7 +1080,7 @@
         <v>82</v>
       </c>
       <c r="T2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U2" s="1" t="s">
         <v>84</v>
@@ -1145,8 +1151,8 @@
       <c r="AQ2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AR2" s="1" t="s">
-        <v>90</v>
+      <c r="AR2" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="AS2" s="1" t="s">
         <v>88</v>
@@ -1167,93 +1173,93 @@
         <v>88</v>
       </c>
       <c r="AY2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="BA2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BB2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="BA2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="BB2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BF2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="BF2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BN2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BW2" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="BH2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BJ2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="BK2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BR2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="BW2" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>76</v>
@@ -1262,13 +1268,13 @@
         <v>77</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" t="s">
         <v>103</v>
-      </c>
-      <c r="I3" t="s">
-        <v>104</v>
       </c>
       <c r="J3" t="s">
         <v>78</v>
@@ -1301,7 +1307,7 @@
         <v>82</v>
       </c>
       <c r="T3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U3" s="1" t="s">
         <v>84</v>
@@ -1372,8 +1378,8 @@
       <c r="AQ3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AR3" s="1" t="s">
-        <v>90</v>
+      <c r="AR3" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="AS3" s="1" t="s">
         <v>88</v>
@@ -1394,93 +1400,93 @@
         <v>88</v>
       </c>
       <c r="AY3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="AZ3" s="1" t="s">
+      <c r="BA3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BF3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BG3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="BA3" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="BB3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD3" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="BE3" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF3" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="BH3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BJ3" s="1" t="s">
+      <c r="BK3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BN3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="BK3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BN3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV3" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="BW3" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>76</v>
@@ -1489,13 +1495,13 @@
         <v>77</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" t="s">
         <v>103</v>
-      </c>
-      <c r="I4" t="s">
-        <v>104</v>
       </c>
       <c r="J4" t="s">
         <v>78</v>
@@ -1528,7 +1534,7 @@
         <v>82</v>
       </c>
       <c r="T4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U4" s="1" t="s">
         <v>84</v>
@@ -1599,8 +1605,8 @@
       <c r="AQ4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AR4" s="1" t="s">
-        <v>90</v>
+      <c r="AR4" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="AS4" s="1" t="s">
         <v>88</v>
@@ -1621,41 +1627,41 @@
         <v>88</v>
       </c>
       <c r="AY4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ4" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="AZ4" s="1" t="s">
+      <c r="BA4" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="BA4" s="1" t="s">
+      <c r="BB4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="BE4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BF4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BG4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="BB4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BF4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BG4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="BH4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BJ4" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="BK4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1690,24 +1696,24 @@
         <v>0</v>
       </c>
       <c r="BV4" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BW4" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>76</v>
@@ -1716,13 +1722,13 @@
         <v>77</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" t="s">
         <v>103</v>
-      </c>
-      <c r="I5" t="s">
-        <v>104</v>
       </c>
       <c r="J5" t="s">
         <v>78</v>
@@ -1755,7 +1761,7 @@
         <v>82</v>
       </c>
       <c r="T5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U5" s="1" t="s">
         <v>84</v>
@@ -1826,115 +1832,115 @@
       <c r="AQ5" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AR5" s="1" t="s">
+      <c r="AR5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AS5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AX5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="BA5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="BB5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="BE5" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AS5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AW5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AX5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY5" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AZ5" s="1" t="s">
+      <c r="BF5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BG5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="BA5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="BB5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="BF5" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BG5" s="1" t="s">
+      <c r="BK5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BN5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW5" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="BH5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BJ5" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="BK5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BN5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BR5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="BW5" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:75" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>76</v>
@@ -1943,13 +1949,13 @@
         <v>77</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" t="s">
         <v>103</v>
-      </c>
-      <c r="I6" t="s">
-        <v>104</v>
       </c>
       <c r="J6" t="s">
         <v>78</v>
@@ -1982,7 +1988,7 @@
         <v>82</v>
       </c>
       <c r="T6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U6" s="1" t="s">
         <v>84</v>
@@ -2053,8 +2059,8 @@
       <c r="AQ6" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AR6" s="1" t="s">
-        <v>90</v>
+      <c r="AR6" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="AS6" s="1" t="s">
         <v>88</v>
@@ -2075,79 +2081,79 @@
         <v>88</v>
       </c>
       <c r="AY6" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AZ6" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="AZ6" s="1" t="s">
+      <c r="BA6" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="BB6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="BE6" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="BA6" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="BB6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BD6" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="BE6" s="1" t="s">
+      <c r="BF6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BG6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="BF6" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BG6" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="BH6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BJ6" s="1" t="s">
+      <c r="BK6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BN6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>0</v>
+      </c>
+      <c r="BV6" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="BK6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BN6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BR6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BS6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BT6" t="s">
-        <v>0</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>0</v>
-      </c>
-      <c r="BV6" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="BW6" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/ResourcesBD/OutletExcel.xlsx
+++ b/ResourcesBD/OutletExcel.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="209">
   <si>
     <t/>
   </si>
@@ -252,9 +252,6 @@
     <t>C14842</t>
   </si>
   <si>
-    <t>002001D05033D10611D33063D95869</t>
-  </si>
-  <si>
     <t>001001</t>
   </si>
   <si>
@@ -396,40 +393,259 @@
     <t>C0012346313</t>
   </si>
   <si>
-    <t>AUTO_OUTLABEE0</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL6550E</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL1B376</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL8DFAD</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLC4087</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLD1A24</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLB6CD6</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL43CFE</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL8AD20</t>
-  </si>
-  <si>
-    <t>AUTO_OUTLBBE7F</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL3BB0F</t>
-  </si>
-  <si>
-    <t>AUTO_OUTL85EC9</t>
+    <t>AUTO_OUTL356D8</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0B258</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4A7E8</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8DD3D</t>
+  </si>
+  <si>
+    <t>002001D01224D10796D33059D95890</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL81728</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5183A</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4E4FE</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2A653</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL07A0A</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL46D6F</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL094A1</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC12A1</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4FE4E</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF8406</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0CE15</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC902E</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL562CE</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL695D1</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD2C7B</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB9E65</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL53E33</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1761A</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL77A77</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6C2F4</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE5512</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3EA0B</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDFF7E</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4A982</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLFB932</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL08ABE</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL44841</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3A825</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDD49A</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC1A2B</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD8BB7</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEE9DF</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC875F</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5D374</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB4235</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8650E</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL98B90</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC293D</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1223C</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA214F</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBBFF0</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL91BFA</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDAEA1</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL360F9</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL92C6B</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF17DE</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC57B5</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL78E73</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL7D614</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1C680</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8EDFE</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE34EB</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6AC6B</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL70D03</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9A18A</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL24915</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL429EC</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBE91E</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1DBB3</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL5A6F6</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL1C73D</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLE112C</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLEE9E6</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL7427B</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA0407</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9B3A7</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB9DDE</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA39FC</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD5570</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBF4C4</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL493F4</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6EBA5</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL29F7E</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL15B62</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCAB3E</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL32DB6</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC6F87</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2AE79</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8FB89</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL86EA5</t>
   </si>
 </sst>
 </file>
@@ -1049,16 +1265,16 @@
     </row>
     <row r="2" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>73</v>
@@ -1078,8 +1294,8 @@
       <c r="J2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>77</v>
+      <c r="K2" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="L2" s="3">
         <v>91.831234800000004</v>
@@ -1088,37 +1304,37 @@
         <v>22.3365528</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="S2" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="S2" t="s" s="0">
+      <c r="V2" t="s" s="0">
         <v>82</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U2" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="V2" t="s" s="0">
-        <v>83</v>
       </c>
       <c r="W2" t="s" s="0">
         <v>75</v>
       </c>
       <c r="X2" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y2" t="s" s="0">
         <v>75</v>
@@ -1127,19 +1343,19 @@
         <v>0</v>
       </c>
       <c r="AA2" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB2" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="AD2" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE2" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AF2" s="1" t="s">
         <v>0</v>
@@ -1154,129 +1370,129 @@
         <v>0</v>
       </c>
       <c r="AJ2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AK2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="AO2" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR2" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AW2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AX2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BC2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AX2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BN2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ2" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="BR2" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="BS2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BT2" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="BD2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="BE2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BG2" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="BH2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BJ2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="BS2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="BT2" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>73</v>
@@ -1296,8 +1512,8 @@
       <c r="J3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>77</v>
+      <c r="K3" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="L3" s="3">
         <v>91.830986199999998</v>
@@ -1306,37 +1522,37 @@
         <v>22.336903199999998</v>
       </c>
       <c r="N3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q3" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="S3" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q3" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="S3" t="s" s="0">
+      <c r="V3" t="s" s="0">
         <v>82</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U3" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="V3" t="s" s="0">
-        <v>83</v>
       </c>
       <c r="W3" t="s" s="0">
         <v>75</v>
       </c>
       <c r="X3" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y3" t="s" s="0">
         <v>75</v>
@@ -1345,19 +1561,19 @@
         <v>0</v>
       </c>
       <c r="AA3" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB3" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="AD3" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE3" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AF3" s="1" t="s">
         <v>0</v>
@@ -1372,77 +1588,77 @@
         <v>0</v>
       </c>
       <c r="AJ3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AK3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN3" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="AO3" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AQ3" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR3" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS3" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU3" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AW3" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="AW3" s="1" t="s">
+      <c r="AX3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="AX3" s="1" t="s">
+      <c r="AY3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BC3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BD3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="AY3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="BB3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="BD3" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="BE3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="BH3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1477,24 +1693,24 @@
         <v>0</v>
       </c>
       <c r="BS3" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="BT3" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>73</v>
@@ -1514,8 +1730,8 @@
       <c r="J4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>77</v>
+      <c r="K4" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="L4" s="3">
         <v>91.831065199999998</v>
@@ -1524,37 +1740,37 @@
         <v>22.336877699999999</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q4" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="S4" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q4" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="S4" t="s" s="0">
+      <c r="V4" t="s" s="0">
         <v>82</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U4" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="V4" t="s" s="0">
-        <v>83</v>
       </c>
       <c r="W4" t="s" s="0">
         <v>75</v>
       </c>
       <c r="X4" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y4" t="s" s="0">
         <v>75</v>
@@ -1563,19 +1779,19 @@
         <v>0</v>
       </c>
       <c r="AA4" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB4" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="AD4" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE4" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AF4" s="1" t="s">
         <v>0</v>
@@ -1590,129 +1806,129 @@
         <v>0</v>
       </c>
       <c r="AJ4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AK4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN4" s="1" t="s">
+      <c r="AO4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR4" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="BB4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AO4" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="AP4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AR4" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="AS4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AU4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AV4" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AW4" s="1" t="s">
+      <c r="BC4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BD4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BE4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="AX4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB4" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="BC4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="BD4" s="1" t="s">
+      <c r="BH4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BN4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="BS4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT4" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="BE4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BG4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BH4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BJ4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BN4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="BS4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT4" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>73</v>
@@ -1732,8 +1948,8 @@
       <c r="J5" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>77</v>
+      <c r="K5" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="L5" s="3">
         <v>91.831235199999995</v>
@@ -1742,37 +1958,37 @@
         <v>22.335977</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q5" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="S5" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q5" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="S5" t="s" s="0">
+      <c r="V5" t="s" s="0">
         <v>82</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U5" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="V5" t="s" s="0">
-        <v>83</v>
       </c>
       <c r="W5" t="s" s="0">
         <v>75</v>
       </c>
       <c r="X5" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y5" t="s" s="0">
         <v>75</v>
@@ -1781,19 +1997,19 @@
         <v>0</v>
       </c>
       <c r="AA5" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB5" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC5" s="2" t="s">
         <v>0</v>
       </c>
       <c r="AD5" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE5" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AF5" s="1" t="s">
         <v>0</v>
@@ -1808,115 +2024,115 @@
         <v>0</v>
       </c>
       <c r="AJ5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AK5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN5" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="AO5" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AP5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AQ5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AR5" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AT5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AU5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AV5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AW5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AW5" s="1" t="s">
+      <c r="AX5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AX5" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AY5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA5" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BB5" s="1" t="s">
+      <c r="BC5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BD5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BE5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="BC5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="BD5" s="1" t="s">
+      <c r="BH5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BN5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="BS5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BT5" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="BE5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BG5" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="BH5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BI5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BJ5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BM5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BN5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BO5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BP5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="BS5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="BT5" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
